--- a/Dotazník.xlsx
+++ b/Dotazník.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29311"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29325"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F74A47E1-E901-4887-B36E-63BEB5239E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{786A6FEF-BB97-4BF2-A874-94398E57811A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="List1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -36,232 +35,8 @@
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="8">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="1"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="4"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="8"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="9"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="13"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="14"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="17"/>
-        </ext>
-      </extLst>
-    </bk>
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="20"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-  <valueMetadata count="8">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-    <bk>
-      <rc t="2" v="1"/>
-    </bk>
-    <bk>
-      <rc t="2" v="2"/>
-    </bk>
-    <bk>
-      <rc t="2" v="3"/>
-    </bk>
-    <bk>
-      <rc t="2" v="4"/>
-    </bk>
-    <bk>
-      <rc t="2" v="5"/>
-    </bk>
-    <bk>
-      <rc t="2" v="6"/>
-    </bk>
-    <bk>
-      <rc t="2" v="7"/>
-    </bk>
-  </valueMetadata>
-</metadata>
-</file>
-
-<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
-<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
-  <environmentDefinition id="{00000000-0000-0000-0000-000000000000}">
-    <initialization>
-      <code/>
-    </initialization>
-  </environmentDefinition>
-  <pythonScripts>
-    <pythonScript>
-      <code>import matplotlib.pyplot as plt
-import numpy as np
-import matplotlib.cm as cm
-import pandas as pd
-import seaborn as sns
-from collections import Counter
-import textwrap</code>
-    </pythonScript>
-    <pythonScript>
-      <code>extraversion_answer= xl(%P2%).values.flatten()
-question_6  = xl(%P3%).values.flatten()
-question_7  = xl(%P4%).values.flatten()
-question_8  = xl(%P5%).values.flatten()
-question_9  = xl(%P6%).values.flatten()
-question_10 = xl(%P7%).values.flatten()
-question_11 = xl(%P8%).values.flatten()
-question_12 = xl(%P9%).values.flatten()
-question_13 = xl(%P10%).values.flatten()
-question_14 = xl(%P11%).values.flatten()
-question_15 = xl(%P12%).values.flatten()
-question_16 = xl(%P13%).values.flatten()
-question_17 = xl(%P14%).values.flatten()
-question_18 = xl(%P15%).values.flatten()
-question_19 = xl(%P16%).values.flatten()
-question_20 = xl(%P17%).values.flatten()
-question_21 = xl(%P18%).values.flatten()
-question_22 = xl(%P19%).values.flatten()
-question_23 = xl(%P20%).values.flatten()
-question_24 = xl(%P21%).values.flatten()
-question_26 = xl(%P22%).values.flatten()
-question_27 = xl(%P23%).values.flatten()
-question_28 = xl(%P24%).values.flatten()
-question_29 = xl(%P25%).values.flatten()
-question_30 = xl(%P26%).values.flatten()</code>
-    </pythonScript>
-    <pythonScript>
-      <code xml:space="preserve">intr = 0
-extr = 0
-komb = 0
-count_answer = len(extraversion_answer)
-for v in extraversion_answer:
-    if v == "Introvert":
-        intr +=1
-    elif v == "Extrovert":
-        extr +=1
-    elif v == "Kombinace obojího":
-        komb +=1
-intr_round = round((intr*100)/count_answer,ndigits=2)
-extr_round = round((extr*100)/count_answer,ndigits=2)
-komb_round = round((komb*100)/count_answer,ndigits=2)
-labels = ['Introvert', 'Extrovert', 'Kombinace obojího']
-sizes = [intr_round, extr_round, komb_round]
-fig, ax = plt.subplots()
-colors = cm.tab20.colors[14:19]
-ax.pie(sizes,labels=labels,autopct='%%1.2f%%%%', shadow=True,colors=colors)
-ax.set(aspect="equal", title='Hypoteza 1')
-plt.show()
-</code>
-    </pythonScript>
-    <pythonScript>
-      <code xml:space="preserve">import matplotlib.pyplot as plt
-from collections import Counter
-introvert_index = [i for i, v in enumerate(extraversion_answer) if v == "Introvert"]
-introvert_question_numbers = [6, 7, 10, 13, 14, 17, 18, 21]
-introvert_question = [question_6, question_7, question_10, question_13,
-                      question_14, question_17, question_18, question_21]
-multi_choice_numbers = [19]
-multi_choice_lists = [question_19]
-top_multi_answers = []
-top_multi_counts = []
-for q in multi_choice_lists:
-    intro_answers = [q[i] for i in introvert_index if q[i]]
-    split_answers = []
-    for ans in intro_answers:
-        split_answers.extend([a.strip() for a in ans.split(';')])
-    top = Counter(split_answers).most_common(1)[0]
-    top_multi_answers.append(top[0])
-    top_multi_counts.append(top[1])
-top_introvert_answer = []
-top_counts = []
-for q in introvert_question:
-    intro_answer = [q[i] for i in introvert_index]
-    top = Counter(intro_answer).most_common(1)[0]
-    top_introvert_answer.append(top[0])
-    top_counts.append(top[1])
-all_numbers = introvert_question_numbers + multi_choice_numbers
-all_counts = top_counts + top_multi_counts
-all_answers = top_introvert_answer + top_multi_answers
-fig, ax = plt.subplots(figsize=(12, 10))
-ax.bar([f"Q{n}" for n in all_numbers], all_counts, color=cm.tab20.colors[3:4])
-for i, txt in enumerate(all_answers):
-    wrapped = "\n".join(textwrap.wrap(txt, 20)) 
-    ax.text(i, all_counts[i] + 0.1, wrapped, ha='center', va='bottom', fontsize=8)
-ax.set_ylabel('Počet odpovědí')
-ax.set_title('Nejčastější odpovědi introvertů na vybrané otázky')
-plt.show()
-</code>
-    </pythonScript>
-    <pythonScript>
-      <code>extravert_index = [i for i, v in enumerate(extraversion_answer) if v == "Extrovert"]</code>
-    </pythonScript>
-    <pythonScript>
-      <code>kombi_index = [i for i, v in enumerate(extraversion_answer) if v == "Kombinace obojího"]</code>
-    </pythonScript>
-  </pythonScripts>
-</python>
-</file>
-
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1735" uniqueCount="396">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="401">
   <si>
     <t>Id</t>
   </si>
@@ -1454,6 +1229,21 @@
   </si>
   <si>
     <t xml:space="preserve">kantyna v kanclu </t>
+  </si>
+  <si>
+    <t>Microsoft Teams;Slack</t>
+  </si>
+  <si>
+    <t>Přímý kontakt s vedením;Profesionální prostředí</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lepší organizační schopnosti kolegů </t>
+  </si>
+  <si>
+    <t xml:space="preserve">kafe zadarmo  </t>
+  </si>
+  <si>
+    <t>vice sick day</t>
   </si>
 </sst>
 </file>
@@ -1489,14 +1279,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="37">
     <dxf>
@@ -1623,343 +1414,9 @@
 </styleSheet>
 </file>
 
-<file path=xl/richData/rdRichValueTypes.xml><?xml version="1.0" encoding="utf-8"?>
-<rvTypesInfo xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <global>
-    <keyFlags>
-      <key name="_Self">
-        <flag name="ExcludeFromFile" value="1"/>
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_DisplayString">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Flags">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Format">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_SubLabel">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Attribution">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Icon">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_Display">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_CanonicalPropertyNames">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-      <key name="_ClassificationId">
-        <flag name="ExcludeFromCalcComparison" value="1"/>
-      </key>
-    </keyFlags>
-  </global>
-</rvTypesInfo>
-</file>
-
-<file path=xl/richData/rdarray.xml><?xml version="1.0" encoding="utf-8"?>
-<arrayData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="5">
-  <a r="11">
-    <v t="r">0</v>
-    <v t="s">Samostatné, vyžadující hluboké zamyšlení</v>
-    <v t="s">Kombinace obou typů</v>
-    <v t="s">Kombinace obou typů</v>
-    <v t="s">Kombinace obou typů</v>
-    <v t="s">...</v>
-    <v t="s">Kombinace obou typů</v>
-    <v t="s">Samostatné, vyžadující hluboké zamyšlení</v>
-    <v t="s">Samostatné, vyžadující hluboké zamyšlení</v>
-    <v t="s">Týmové, zahrnující spolupráci s ostatními</v>
-    <v t="s">Kombinace obou typů</v>
-  </a>
-  <a r="2">
-    <v>431</v>
-    <v>409</v>
-  </a>
-  <a r="2">
-    <v>1010</v>
-    <v>836</v>
-  </a>
-  <a r="7">
-    <v>2</v>
-    <v>12</v>
-    <v>14</v>
-    <v>21</v>
-    <v>24</v>
-    <v>31</v>
-    <v>48</v>
-  </a>
-  <a r="11">
-    <v>1</v>
-    <v>4</v>
-    <v>5</v>
-    <v>9</v>
-    <v>10</v>
-    <v t="s">...</v>
-    <v>37</v>
-    <v>42</v>
-    <v>43</v>
-    <v>45</v>
-    <v>49</v>
-  </a>
-</arrayData>
-</file>
-
-<file path=xl/richData/rdrichvalue.xml><?xml version="1.0" encoding="utf-8"?>
-<rvData xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="21">
-  <rv s="0">
-    <fb>0</fb>
-    <v>0</v>
-  </rv>
-  <rv s="1">
-    <fb>0</fb>
-    <v>&lt;class 'NoneType'&gt;</v>
-    <v>NoneType</v>
-    <v>None</v>
-    <v>0</v>
-    <v>1</v>
-  </rv>
-  <rv s="2">
-    <v>0</v>
-  </rv>
-  <rv s="3">
-    <v>ndarray</v>
-    <v>3</v>
-    <v>2</v>
-  </rv>
-  <rv s="1">
-    <v>&lt;class 'numpy.ndarray'&gt;</v>
-    <v>ndarray</v>
-    <v>[None 'Samostatné, vyžadující hluboké zamyšlení' 'Kombinace obou typů'
- 'Kombinace obou typů' 'Kombinace obou typů' 'Kombinace obou typů'
- 'Samostatné, vyžadující hluboké zamyšlení'
- 'Samostatné, vyžadující hluboké zamyšlení'
- 'Samostatné, vyžadující h...</v>
-    <v>3</v>
-    <v>1</v>
-  </rv>
-  <rv s="4">
-    <v>0</v>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>1</v>
-  </rv>
-  <rv s="5">
-    <v>Image</v>
-    <v>4</v>
-    <v>5</v>
-    <v>6</v>
-  </rv>
-  <rv s="1">
-    <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
-    <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=431x409 at 0x7F5DBE316AE0&gt;</v>
-    <v>7</v>
-    <v>1</v>
-  </rv>
-  <rv s="4">
-    <v>0</v>
-    <v>3</v>
-  </rv>
-  <rv s="4">
-    <v>1</v>
-    <v>9</v>
-  </rv>
-  <rv s="2">
-    <v>2</v>
-  </rv>
-  <rv s="5">
-    <v>Image</v>
-    <v>4</v>
-    <v>10</v>
-    <v>11</v>
-  </rv>
-  <rv s="1">
-    <v>&lt;class 'PIL.PngImagePlugin.PngImageFile'&gt;</v>
-    <v>PngImageFile</v>
-    <v>&lt;PIL.PngImagePlugin.PngImageFile image mode=RGBA size=1010x836 at 0x7F5DBE0ADD90&gt;</v>
-    <v>12</v>
-    <v>1</v>
-  </rv>
-  <rv s="4">
-    <v>1</v>
-    <v>3</v>
-  </rv>
-  <rv s="2">
-    <v>3</v>
-  </rv>
-  <rv s="3">
-    <v>list</v>
-    <v>6</v>
-    <v>15</v>
-  </rv>
-  <rv s="1">
-    <v>&lt;class 'list'&gt;</v>
-    <v>list</v>
-    <v>[2, 12, 14, 21, 24, 31, 48]</v>
-    <v>16</v>
-    <v>1</v>
-  </rv>
-  <rv s="2">
-    <v>4</v>
-  </rv>
-  <rv s="3">
-    <v>list</v>
-    <v>8</v>
-    <v>18</v>
-  </rv>
-  <rv s="1">
-    <v>&lt;class 'list'&gt;</v>
-    <v>list</v>
-    <v>[1, 4, 5, 9, 10, 13, 17, 25, 26, 29, 32, 37, 42, 43, 45, 49]</v>
-    <v>19</v>
-    <v>1</v>
-  </rv>
-</rvData>
-</file>
-
-<file path=xl/richData/rdrichvaluestructure.xml><?xml version="1.0" encoding="utf-8"?>
-<rvStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" count="6">
-  <s t="_formattednumber">
-    <k n="_Format" t="spb"/>
-  </s>
-  <s t="_python">
-    <k n="Python_type" t="s"/>
-    <k n="Python_typeName" t="s"/>
-    <k n="Python_str" t="s"/>
-    <k n="preview" t="r"/>
-    <k n="_Provider" t="spb"/>
-  </s>
-  <s t="_array">
-    <k n="array" t="a"/>
-  </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_ViewInfo" t="spb"/>
-    <k n="arrayPreview" t="r"/>
-  </s>
-  <s t="_localImage">
-    <k n="_rvRel:LocalImageIdentifier" t="i"/>
-    <k n="CalcOrigin" t="i"/>
-  </s>
-  <s t="_entity">
-    <k n="_DisplayString" t="s"/>
-    <k n="_Format" t="spb"/>
-    <k n="image" t="r"/>
-    <k n="size" t="r"/>
-  </s>
-</rvStructures>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybag.xml><?xml version="1.0" encoding="utf-8"?>
-<supportingPropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2">
-  <spbData count="9">
-    <spb s="0">
-      <v>1</v>
-    </spb>
-    <spb s="1">
-      <v>https://www.anaconda.com/excel</v>
-      <v>https://res.cdn.office.net/officepysvc/prod-service/anacondalogo.png</v>
-      <v>Python provided by Anaconda</v>
-    </spb>
-    <spb s="2">
-      <v>50</v>
-      <v>1</v>
-      <v>ndarray</v>
-      <v>arrayPreview</v>
-    </spb>
-    <spb s="3">
-      <v>2</v>
-    </spb>
-    <spb s="4">
-      <v>2</v>
-    </spb>
-    <spb s="2">
-      <v>7</v>
-      <v>1</v>
-      <v>list</v>
-      <v>arrayPreview</v>
-    </spb>
-    <spb s="3">
-      <v>5</v>
-    </spb>
-    <spb s="2">
-      <v>16</v>
-      <v>1</v>
-      <v>list</v>
-      <v>arrayPreview</v>
-    </spb>
-    <spb s="3">
-      <v>7</v>
-    </spb>
-  </spbData>
-</supportingPropertyBags>
-</file>
-
-<file path=xl/richData/rdsupportingpropertybagstructure.xml><?xml version="1.0" encoding="utf-8"?>
-<spbStructures xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" count="5">
-  <s>
-    <k n="_Self" t="i"/>
-  </s>
-  <s>
-    <k n="link" t="s"/>
-    <k n="logo" t="s"/>
-    <k n="name" t="s"/>
-  </s>
-  <s>
-    <k n="drw" t="i"/>
-    <k n="dcol" t="i"/>
-    <k n="name" t="s"/>
-    <k n="array" t="s"/>
-  </s>
-  <s>
-    <k n="ArrayCardInfo" t="spb"/>
-  </s>
-  <s>
-    <k n="image" t="i"/>
-  </s>
-</spbStructures>
-</file>
-
-<file path=xl/richData/richStyles.xml><?xml version="1.0" encoding="utf-8"?>
-<richStyleSheet xmlns="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" mc:Ignorable="x">
-  <dxfs count="1">
-    <x:dxf>
-      <x:numFmt numFmtId="0" formatCode="General"/>
-    </x:dxf>
-  </dxfs>
-  <richProperties>
-    <rPr n="NumberFormat" t="s"/>
-    <rPr n="IsHeroField" t="b"/>
-  </richProperties>
-  <richStyles>
-    <rSty dxfid="0">
-      <rpv i="0">0;-0;"None"</rpv>
-    </rSty>
-    <rSty>
-      <rpv i="1">1</rpv>
-    </rSty>
-  </richStyles>
-</richStyleSheet>
-</file>
-
-<file path=xl/richData/richValueRel.xml><?xml version="1.0" encoding="utf-8"?>
-<richValueRels xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/richvaluerel" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <rel r:id="rId1"/>
-  <rel r:id="rId2"/>
-</richValueRels>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AM51" totalsRowShown="0">
-  <autoFilter ref="A1:AM51" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AM52" totalsRowShown="0">
+  <autoFilter ref="A1:AM52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="39">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="36">
       <extLst>
@@ -2238,7 +1695,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="tAviCnY6L0ykJOcTgjkxwG7J3EwVANhLiTfAS4_SiPpUN0FMQ1g2Q1IwT1FTOTRSTkVTQjZIM05JRi4u" maxResponseId="50" latestEventMarker="57">
+      <xlmsforms:msForm id="tAviCnY6L0ykJOcTgjkxwG7J3EwVANhLiTfAS4_SiPpUN0FMQ1g2Q1IwT1FTOTRSTkVTQjZIM05JRi4u" isFormConnected="1" maxResponseId="51" latestEventMarker="58">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -2581,7 +2038,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM51"/>
+  <dimension ref="A1:AM52"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="9" width="20" bestFit="1" customWidth="1"/>
@@ -2919,7 +2376,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:39">
+    <row r="4" spans="1:39" ht="15.75" customHeight="1">
       <c r="A4">
         <v>3</v>
       </c>
@@ -8447,81 +7904,128 @@
         <v>173</v>
       </c>
     </row>
+    <row r="52" spans="1:39">
+      <c r="A52" s="4">
+        <v>51</v>
+      </c>
+      <c r="B52" s="1">
+        <v>45935.555729166699</v>
+      </c>
+      <c r="C52" s="1">
+        <v>45935.559907407398</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E52" s="2"/>
+      <c r="F52" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="L52" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="N52" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="O52" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="P52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="Q52" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="R52" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="S52" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="T52" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="U52" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="V52" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="W52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="X52" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="Y52" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="Z52" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="AA52" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="AB52" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="AC52" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="AD52" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AE52" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AF52" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AG52" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH52" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="AI52" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AJ52" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="AK52" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="AL52" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="AM52" s="2" t="s">
+        <v>400</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <headerFooter>
-    <oddFooter>&amp;L_x000D_&amp;1#&amp;"Aptos"&amp;9&amp;K008000 Interní</oddFooter>
-  </headerFooter>
   <tableParts count="1">
     <tablePart r:id="rId2"/>
   </tableParts>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{145CFC6E-1EA2-418E-ACCA-0338EBF3D6BD}">
-  <dimension ref="A1:B12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="22" customWidth="1"/>
-    <col min="2" max="2" width="104" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" customWidth="1"/>
-    <col min="8" max="8" width="11.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" cm="1" vm="1">
-        <f t="array" ref="A1">_xlfn._xlws.PY(0,1)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="e" cm="1" vm="2">
-        <f t="array" ref="A3">_xlfn._xlws.PY(1,1,Sheet1!AE2:AE51,Sheet1!L2:L51,Sheet1!M2:M51,Sheet1!N2:N51,Sheet1!O2:O51,Sheet1!P2:P51,Sheet1!Q2:Q51,Sheet1!R2:R51,Sheet1!S2:S51,Sheet1!T2:T51,Sheet1!U2:U51,Sheet1!V2:V51,Sheet1!W2:W51,Sheet1!X2:X51,Sheet1!Y2:Y51,Sheet1!Z2:Z51,Sheet1!AA2:AA51,Sheet1!AB2:AB51,Sheet1!AC2:AC51,Sheet1!AD2:AD51,Sheet1!AF2:AF51,Sheet1!AG2:AG51,Sheet1!AH2:AH51,Sheet1!AI2:AI51,Sheet1!AJ2:AJ51)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" ht="276.75" customHeight="1">
-      <c r="A6" t="e" cm="1" vm="3">
-        <f t="array" ref="A6">_xlfn._xlws.PY(2,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B6" t="e" cm="1" vm="4">
-        <f t="array" ref="B6">_FV(A6,"image",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" hidden="1"/>
-    <row r="8" spans="1:2" ht="409.5" customHeight="1">
-      <c r="A8" t="e" cm="1" vm="5">
-        <f t="array" ref="A8">_xlfn._xlws.PY(3,1)</f>
-        <v>#VALUE!</v>
-      </c>
-      <c r="B8" t="e" cm="1" vm="6">
-        <f t="array" ref="B8">_FV(A8,"image",TRUE)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" t="e" cm="1" vm="7">
-        <f t="array" ref="A10">_xlfn._xlws.PY(4,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" ht="14.25" customHeight="1">
-      <c r="A12" t="e" cm="1" vm="8">
-        <f t="array" ref="A12">_xlfn._xlws.PY(5,1)</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
-<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{30e822eb-17eb-4574-b08c-2c496d08d42f}" enabled="1" method="Standard" siteId="{deb3a78c-2111-476d-8e51-0b43101108e1}" removed="0"/>
-</clbl:labelList>
 </file>
--- a/Dotazník.xlsx
+++ b/Dotazník.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\qinzen\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/traum/Projects/bp/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{786A6FEF-BB97-4BF2-A874-94398E57811A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{211438C3-951F-DD4B-B410-367397EADE37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="13905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,6 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
@@ -36,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1770" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1771" uniqueCount="402">
   <si>
     <t>Id</t>
   </si>
@@ -1244,14 +1243,25 @@
   </si>
   <si>
     <t>vice sick day</t>
+  </si>
+  <si>
+    <t>Kolika projektů jste se zúčastnil(a)?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -1279,17 +1289,24 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="22" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normální" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="37">
+  <dxfs count="38">
+    <dxf>
+      <numFmt numFmtId="1" formatCode="0"/>
+    </dxf>
     <dxf>
       <numFmt numFmtId="30" formatCode="@"/>
     </dxf>
@@ -1415,10 +1432,16 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AM52" totalsRowShown="0">
-  <autoFilter ref="A1:AM52" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
-  <tableColumns count="39">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="36">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="OfficeForms.Table" displayName="OfficeForms.Table" ref="A1:AN52" totalsRowShown="0">
+  <autoFilter ref="A1:AN52" xr:uid="{00000000-0009-0000-0100-000001000000}">
+    <filterColumn colId="30">
+      <filters>
+        <filter val="Extrovert"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <tableColumns count="40">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Id" dataDxfId="37">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="id"/>
@@ -1439,255 +1462,262 @@
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-mail" dataDxfId="35">
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="E-mail" dataDxfId="36">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responder"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Jméno" dataDxfId="34">
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="Jméno" dataDxfId="35">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="responderName"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Language" dataDxfId="33">
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="Language" dataDxfId="34">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="submitLanguage"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Jaká je Vaše pracovní pozice?" dataDxfId="32">
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="Jaká je Vaše pracovní pozice?" dataDxfId="33">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re017a6b1fe9d4ca4af1db7f56ba763ef"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Jaká je Vaše úroveň pracovních zkušeností?" dataDxfId="31">
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="Jaká je Vaše úroveň pracovních zkušeností?" dataDxfId="32">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5e74d96c90e9420a81d5b3801e9662dc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Jaký je typ Vašeho zaměstnání?" dataDxfId="30">
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="Jaký je typ Vašeho zaměstnání?" dataDxfId="31">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0889f069538245539dc845d1a355403b"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="30" xr3:uid="{629AC853-D9EC-4533-8393-862D86A806B0}" name="Jaká je velikost firmy, ve které pracujete?" dataDxfId="29">
+    <tableColumn id="30" xr3:uid="{629AC853-D9EC-4533-8393-862D86A806B0}" name="Jaká je velikost firmy, ve které pracujete?" dataDxfId="30">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r48b4f690ca3c4bd0957755fad7c1dd92"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="31" xr3:uid="{88CE2A87-EA8F-488C-A9ED-254B29F3A015}" name=" Kde se nachází hlavní sídlo Vaší firmy?" dataDxfId="28">
+    <tableColumn id="31" xr3:uid="{88CE2A87-EA8F-488C-A9ED-254B29F3A015}" name=" Kde se nachází hlavní sídlo Vaší firmy?" dataDxfId="29">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r1712483fbdc749b1b633070463b18aaa"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Jak často pracujete na dálku?" dataDxfId="27">
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="Jak často pracujete na dálku?" dataDxfId="28">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb5d645b4cae9413aa1dd60955fa4976a"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Jak hodnotíte svou produktivitu při práci na dálku ve srovnání s prací v kanceláři?" dataDxfId="26">
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="Jak hodnotíte svou produktivitu při práci na dálku ve srovnání s prací v kanceláři?" dataDxfId="27">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r3131fcb31c0e40f196c0a8dfffec2694"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Co vás nejvíce podporuje v udržení produktivity při práci na dálku?" dataDxfId="25">
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="Co vás nejvíce podporuje v udržení produktivity při práci na dálku?" dataDxfId="26">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0b6f0d383a5b483c9ff0912dd2f0129f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Jaké překážky nejvíce ovlivňují Vaši produktivitu při práci na dálku?" dataDxfId="24">
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="Jaké překážky nejvíce ovlivňují Vaši produktivitu při práci na dálku?" dataDxfId="25">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rb52dc15cf0594660bebfc170436d86bc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Jak hodnotíte efektivitu komunikace s kolegy při práci na dálku?" dataDxfId="23">
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="Jak hodnotíte efektivitu komunikace s kolegy při práci na dálku?" dataDxfId="24">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r151e741948554431abd76673b59ba6e0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Jaké nástroje nejčastěji používáte pro komunikaci při práci na dálku? (vyberte všechny relevantní odpovědi)" dataDxfId="22">
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="Jaké nástroje nejčastěji používáte pro komunikaci při práci na dálku? (vyberte všechny relevantní odpovědi)" dataDxfId="23">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="ra345f6095a5447c789fe776c50f83bdc"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Jaký je podle Vás hlavní problém při komunikaci na dálku?" dataDxfId="21">
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="Jaký je podle Vás hlavní problém při komunikaci na dálku?" dataDxfId="22">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r059c79739a2944e6bd7c18f385137489"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name=" Jak často pracujete v kanceláři?" dataDxfId="20">
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name=" Jak často pracujete v kanceláři?" dataDxfId="21">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r24ea0155af57445d92e110e7db3c242c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jak hodnotíte svou produktivitu při práci v kanceláři?" dataDxfId="19">
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="Jak hodnotíte svou produktivitu při práci v kanceláři?" dataDxfId="20">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5c426ccda8784545b84fb00f21f5998f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name=" Jaké faktory Vám v kanceláři nejvíce pomáhají být produktivní?" dataDxfId="18">
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name=" Jaké faktory Vám v kanceláři nejvíce pomáhají být produktivní?" dataDxfId="19">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r41597497b0b342c1b3da5ae7de2116bf"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Jaké překážky nejvíce ovlivňují Vaši produktivitu při práci v kanceláři?_x000a_" dataDxfId="17">
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="Jaké překážky nejvíce ovlivňují Vaši produktivitu při práci v kanceláři?_x000a_" dataDxfId="18">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="re3d5016bc86c4698893a1e54c687c1b0"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Jak hodnotíte efektivitu komunikace s kolegy v kanceláři?_x000a_" dataDxfId="16">
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="Jak hodnotíte efektivitu komunikace s kolegy v kanceláři?_x000a_" dataDxfId="17">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdbaaea2c8337465ebb52b992a5d72242"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ve kterém prostředí cítíte větší motivaci k práci?" dataDxfId="15">
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="Ve kterém prostředí cítíte větší motivaci k práci?" dataDxfId="16">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r0a935d7a84234ed582a91e299debe2ac"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Jaké faktory Vás nejvíce motivují při práci v obou prostředích?" dataDxfId="14">
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="Jaké faktory Vás nejvíce motivují při práci v obou prostředích?" dataDxfId="15">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd1ec2526a44f4c99b2fa8a4e245a3e30"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="32" xr3:uid="{993C96F6-88CA-4499-9194-389F48EE675F}" name="Jaké faktory Vás nejvíce motivují při práci v kanceláři?" dataDxfId="13">
+    <tableColumn id="32" xr3:uid="{993C96F6-88CA-4499-9194-389F48EE675F}" name="Jaké faktory Vás nejvíce motivují při práci v kanceláři?" dataDxfId="14">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r24080277fe19433db8de87a7e4690b8c"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Jak hodnotíte rovnováhu mezi pracovním a osobním životem v obou prostředích?" dataDxfId="12">
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="Jak hodnotíte rovnováhu mezi pracovním a osobním životem v obou prostředích?" dataDxfId="13">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rcbf17996383e4ceda574c066f2668315"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="33" xr3:uid="{D3528BDA-503D-436B-AC33-7E5A8EAD47F1}" name="Jak hodnotíte rovnováhu mezi pracovním a osobním životem při práci v kanceláři?" dataDxfId="11">
+    <tableColumn id="33" xr3:uid="{D3528BDA-503D-436B-AC33-7E5A8EAD47F1}" name="Jak hodnotíte rovnováhu mezi pracovním a osobním životem při práci v kanceláři?" dataDxfId="12">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5df806b6c1c440be8c62938e50a89ef7"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Máte při práci na dálku nebo v kanceláři větší stres?_x000a_" dataDxfId="10">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="Máte při práci na dálku nebo v kanceláři větší stres?_x000a_" dataDxfId="11">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r9596320f76b64c36a232f4d37be4dd99"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Jak byste hodnotili celkový vliv obou prostředí na kvalitu Vašeho pracovního života?" dataDxfId="9">
+    <tableColumn id="26" xr3:uid="{00000000-0010-0000-0000-00001A000000}" name="Jak byste hodnotili celkový vliv obou prostředí na kvalitu Vašeho pracovního života?" dataDxfId="10">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r47bfd1180c5e4d62a677ee8ce2580be6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="34" xr3:uid="{66977EF9-1F8F-4D5A-B3B0-F8B5DA66FDA5}" name="Považujete se spíše za introverta nebo extroverta?" dataDxfId="8">
+    <tableColumn id="34" xr3:uid="{66977EF9-1F8F-4D5A-B3B0-F8B5DA66FDA5}" name="Považujete se spíše za introverta nebo extroverta?" dataDxfId="9">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rd2fa8f3fb5c0420f9f948b6669b8a434"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="35" xr3:uid="{EE33C134-1F2C-49EF-9BCD-CD215BECB356}" name="Jak byste popsali svůj přístup k ostatním lidem?" dataDxfId="7">
+    <tableColumn id="35" xr3:uid="{EE33C134-1F2C-49EF-9BCD-CD215BECB356}" name="Jak byste popsali svůj přístup k ostatním lidem?" dataDxfId="8">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5de9c1c695354f12b7deee09b7e7e811"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="36" xr3:uid="{C6E31681-3E12-4454-A4C1-1D64EDCDB082}" name="Jak byste hodnotili svůj přístup k povinnostem a organizaci práce?" dataDxfId="6">
+    <tableColumn id="36" xr3:uid="{C6E31681-3E12-4454-A4C1-1D64EDCDB082}" name="Jak byste hodnotili svůj přístup k povinnostem a organizaci práce?" dataDxfId="7">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r5b2132ba06414d449adf1bf94bb2672f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="37" xr3:uid="{3306804F-A849-4849-8AF2-456556022928}" name="Jak obvykle reagujete na stresové situace?" dataDxfId="5">
+    <tableColumn id="37" xr3:uid="{3306804F-A849-4849-8AF2-456556022928}" name="Jak obvykle reagujete na stresové situace?" dataDxfId="6">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rbe06260138ae42599cf85ed7adf2f5f8"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="38" xr3:uid="{8EA11C06-01BC-4BA3-9881-A886EEABB2A1}" name="Jak se stavíte k novým myšlenkám a zkušenostem?" dataDxfId="4">
+    <tableColumn id="38" xr3:uid="{8EA11C06-01BC-4BA3-9881-A886EEABB2A1}" name="Jak se stavíte k novým myšlenkám a zkušenostem?" dataDxfId="5">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r49bddcf7e6de488aaed9bc152c2b3819"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="39" xr3:uid="{320C9662-00F7-4F34-BB69-CE4468976010}" name="Jaký typ úkolů Vás nejvíce motivuje?" dataDxfId="3">
+    <tableColumn id="39" xr3:uid="{320C9662-00F7-4F34-BB69-CE4468976010}" name="Jaký typ úkolů Vás nejvíce motivuje?" dataDxfId="4">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r52c621e0641b49fd945377649c9aa35f"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name=" Jaké změny by podle Vás mohly zlepšit práci na dálku ve Vašem týmu nebo organizaci?" dataDxfId="2">
+    <tableColumn id="27" xr3:uid="{00000000-0010-0000-0000-00001B000000}" name=" Jaké změny by podle Vás mohly zlepšit práci na dálku ve Vašem týmu nebo organizaci?" dataDxfId="3">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r58f67c2e7c5d43dcbae993f2627a46d6"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Jaké změny by podle Vás mohly zlepšit práci v kanceláři ve Vašem týmu nebo organizaci?_x000a_" dataDxfId="1">
+    <tableColumn id="28" xr3:uid="{00000000-0010-0000-0000-00001C000000}" name="Jaké změny by podle Vás mohly zlepšit práci v kanceláři ve Vašem týmu nebo organizaci?_x000a_" dataDxfId="2">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="r133e0afa10b040609a4c4b24ee3d4488"/>
         </ext>
       </extLst>
     </tableColumn>
-    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name=" Jaké aktivity nebo metody by mohly podpořit týmovou soudržnost bez ohledu na prostředí?_x000a_" dataDxfId="0">
+    <tableColumn id="29" xr3:uid="{00000000-0010-0000-0000-00001D000000}" name=" Jaké aktivity nebo metody by mohly podpořit týmovou soudržnost bez ohledu na prostředí?_x000a_" dataDxfId="1">
       <extLst>
         <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
           <xlmsforms:question id="rdd7fa82787734cbba132af06f447cdbc"/>
+        </ext>
+      </extLst>
+    </tableColumn>
+    <tableColumn id="40" xr3:uid="{ED676A0F-782B-4D13-A58F-E5A0C98A8900}" name="Kolika projektů jste se zúčastnil(a)?" dataDxfId="0">
+      <extLst>
+        <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{FCC71383-01E1-4257-9335-427F07BE8D7F}">
+          <xlmsforms:question id="r5262611231f742dabcacc3e3067c8f13"/>
         </ext>
       </extLst>
     </tableColumn>
@@ -1695,7 +1725,7 @@
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
   <extLst>
     <ext xmlns:xlmsforms="http://schemas.microsoft.com/office/spreadsheetml/2023/msForms" uri="{839C7E11-91E4-4DBD-9C5D-0DEA604FA9AC}">
-      <xlmsforms:msForm id="tAviCnY6L0ykJOcTgjkxwG7J3EwVANhLiTfAS4_SiPpUN0FMQ1g2Q1IwT1FTOTRSTkVTQjZIM05JRi4u" isFormConnected="1" maxResponseId="51" latestEventMarker="58">
+      <xlmsforms:msForm id="tAviCnY6L0ykJOcTgjkxwG7J3EwVANhLiTfAS4_SiPpUN0FMQ1g2Q1IwT1FTOTRSTkVTQjZIM05JRi4u" isFormConnected="1" maxResponseId="51" latestEventMarker="62">
         <xlmsforms:syncedQuestionId>id</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>startDate</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>submitDate</xlmsforms:syncedQuestionId>
@@ -1735,6 +1765,7 @@
         <xlmsforms:syncedQuestionId>rbe06260138ae42599cf85ed7adf2f5f8</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r49bddcf7e6de488aaed9bc152c2b3819</xlmsforms:syncedQuestionId>
         <xlmsforms:syncedQuestionId>r52c621e0641b49fd945377649c9aa35f</xlmsforms:syncedQuestionId>
+        <xlmsforms:syncedQuestionId>r5262611231f742dabcacc3e3067c8f13</xlmsforms:syncedQuestionId>
       </xlmsforms:msForm>
     </ext>
   </extLst>
@@ -2038,8 +2069,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AM52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:AN52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="9" width="20" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="19" customWidth="1"/>
@@ -2049,12 +2080,13 @@
     <col min="28" max="28" width="19" customWidth="1"/>
     <col min="29" max="29" width="20" bestFit="1" customWidth="1"/>
     <col min="31" max="36" width="19" customWidth="1"/>
-    <col min="37" max="37" width="86.7109375" customWidth="1"/>
-    <col min="38" max="38" width="59.7109375" customWidth="1"/>
+    <col min="37" max="37" width="86.6640625" customWidth="1"/>
+    <col min="38" max="38" width="59.6640625" customWidth="1"/>
     <col min="39" max="39" width="107" customWidth="1"/>
+    <col min="40" max="40" width="28.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39">
+    <row r="1" spans="1:40" ht="16" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -2172,8 +2204,11 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
+      <c r="AN1" s="4" t="s">
+        <v>401</v>
+      </c>
     </row>
-    <row r="2" spans="1:39" ht="21.75" customHeight="1">
+    <row r="2" spans="1:40" ht="21.75" hidden="1" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>1</v>
       </c>
@@ -2258,8 +2293,11 @@
       <c r="AM2" t="s">
         <v>63</v>
       </c>
+      <c r="AN2" s="5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:39">
+    <row r="3" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2375,8 +2413,11 @@
       <c r="AM3" s="2" t="s">
         <v>86</v>
       </c>
+      <c r="AN3" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" ht="15.75" customHeight="1">
+    <row r="4" spans="1:40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2490,8 +2531,11 @@
       <c r="AM4" s="2" t="s">
         <v>112</v>
       </c>
+      <c r="AN4" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="5" spans="1:39">
+    <row r="5" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2603,8 +2647,11 @@
         <v>124</v>
       </c>
       <c r="AM5" s="2"/>
+      <c r="AN5" s="5">
+        <v>6</v>
+      </c>
     </row>
-    <row r="6" spans="1:39">
+    <row r="6" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2720,8 +2767,11 @@
       <c r="AM6" s="2" t="s">
         <v>139</v>
       </c>
+      <c r="AN6" s="5">
+        <v>15</v>
+      </c>
     </row>
-    <row r="7" spans="1:39">
+    <row r="7" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2837,8 +2887,11 @@
       <c r="AM7" s="2" t="s">
         <v>153</v>
       </c>
+      <c r="AN7" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="8" spans="1:39">
+    <row r="8" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2954,8 +3007,11 @@
       <c r="AM8" s="2" t="s">
         <v>162</v>
       </c>
+      <c r="AN8" s="5">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:39">
+    <row r="9" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -3071,8 +3127,11 @@
       <c r="AM9" s="2" t="s">
         <v>173</v>
       </c>
+      <c r="AN9" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="10" spans="1:39">
+    <row r="10" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -3188,8 +3247,11 @@
       <c r="AM10" s="2" t="s">
         <v>179</v>
       </c>
+      <c r="AN10" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="11" spans="1:39">
+    <row r="11" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -3305,8 +3367,11 @@
       <c r="AM11" s="2" t="s">
         <v>190</v>
       </c>
+      <c r="AN11" s="5">
+        <v>17</v>
+      </c>
     </row>
-    <row r="12" spans="1:39">
+    <row r="12" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -3420,8 +3485,11 @@
         <v>199</v>
       </c>
       <c r="AM12" s="2"/>
+      <c r="AN12" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="13" spans="1:39">
+    <row r="13" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -3537,8 +3605,11 @@
       <c r="AM13" s="2" t="s">
         <v>208</v>
       </c>
+      <c r="AN13" s="5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="14" spans="1:39">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -3654,8 +3725,11 @@
       <c r="AM14" s="2" t="s">
         <v>218</v>
       </c>
+      <c r="AN14" s="5">
+        <v>12</v>
+      </c>
     </row>
-    <row r="15" spans="1:39">
+    <row r="15" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -3771,8 +3845,11 @@
       <c r="AM15" s="2" t="s">
         <v>229</v>
       </c>
+      <c r="AN15" s="5">
+        <v>6</v>
+      </c>
     </row>
-    <row r="16" spans="1:39">
+    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -3888,8 +3965,11 @@
       <c r="AM16" s="2" t="s">
         <v>237</v>
       </c>
+      <c r="AN16" s="5">
+        <v>15</v>
+      </c>
     </row>
-    <row r="17" spans="1:39">
+    <row r="17" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A17">
         <v>16</v>
       </c>
@@ -4005,8 +4085,11 @@
       <c r="AM17" s="2" t="s">
         <v>244</v>
       </c>
+      <c r="AN17" s="5">
+        <v>7</v>
+      </c>
     </row>
-    <row r="18" spans="1:39">
+    <row r="18" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A18">
         <v>17</v>
       </c>
@@ -4122,8 +4205,11 @@
       <c r="AM18" s="2" t="s">
         <v>248</v>
       </c>
+      <c r="AN18" s="5">
+        <v>8</v>
+      </c>
     </row>
-    <row r="19" spans="1:39">
+    <row r="19" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A19">
         <v>18</v>
       </c>
@@ -4239,8 +4325,11 @@
       <c r="AM19" s="2" t="s">
         <v>253</v>
       </c>
+      <c r="AN19" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="20" spans="1:39">
+    <row r="20" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A20">
         <v>19</v>
       </c>
@@ -4356,8 +4445,11 @@
       <c r="AM20" s="2" t="s">
         <v>257</v>
       </c>
+      <c r="AN20" s="6">
+        <v>13</v>
+      </c>
     </row>
-    <row r="21" spans="1:39">
+    <row r="21" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A21">
         <v>20</v>
       </c>
@@ -4467,8 +4559,11 @@
       <c r="AK21" s="2"/>
       <c r="AL21" s="2"/>
       <c r="AM21" s="2"/>
+      <c r="AN21" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="22" spans="1:39">
+    <row r="22" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A22">
         <v>21</v>
       </c>
@@ -4584,8 +4679,11 @@
       <c r="AM22" s="2" t="s">
         <v>267</v>
       </c>
+      <c r="AN22" s="5">
+        <v>8</v>
+      </c>
     </row>
-    <row r="23" spans="1:39">
+    <row r="23" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A23">
         <v>22</v>
       </c>
@@ -4701,8 +4799,11 @@
       <c r="AM23" s="2" t="s">
         <v>272</v>
       </c>
+      <c r="AN23" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="24" spans="1:39">
+    <row r="24" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A24">
         <v>23</v>
       </c>
@@ -4818,8 +4919,11 @@
       <c r="AM24" s="2" t="s">
         <v>283</v>
       </c>
+      <c r="AN24" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="25" spans="1:39">
+    <row r="25" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A25">
         <v>24</v>
       </c>
@@ -4935,8 +5039,11 @@
       <c r="AM25" s="2" t="s">
         <v>294</v>
       </c>
+      <c r="AN25" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="26" spans="1:39">
+    <row r="26" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A26">
         <v>25</v>
       </c>
@@ -5052,8 +5159,11 @@
       <c r="AM26" s="2" t="s">
         <v>299</v>
       </c>
+      <c r="AN26" s="5">
+        <v>20</v>
+      </c>
     </row>
-    <row r="27" spans="1:39">
+    <row r="27" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A27">
         <v>26</v>
       </c>
@@ -5163,8 +5273,11 @@
       <c r="AK27" s="2"/>
       <c r="AL27" s="2"/>
       <c r="AM27" s="2"/>
+      <c r="AN27" s="5">
+        <v>15</v>
+      </c>
     </row>
-    <row r="28" spans="1:39">
+    <row r="28" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A28">
         <v>27</v>
       </c>
@@ -5280,8 +5393,11 @@
       <c r="AM28" s="2" t="s">
         <v>307</v>
       </c>
+      <c r="AN28" s="5">
+        <v>14</v>
+      </c>
     </row>
-    <row r="29" spans="1:39">
+    <row r="29" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A29">
         <v>28</v>
       </c>
@@ -5397,8 +5513,11 @@
       <c r="AM29" s="2" t="s">
         <v>316</v>
       </c>
+      <c r="AN29" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="30" spans="1:39">
+    <row r="30" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A30">
         <v>29</v>
       </c>
@@ -5514,8 +5633,11 @@
       <c r="AM30" s="2" t="s">
         <v>325</v>
       </c>
+      <c r="AN30" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="31" spans="1:39">
+    <row r="31" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A31">
         <v>30</v>
       </c>
@@ -5625,8 +5747,11 @@
       <c r="AK31" s="2"/>
       <c r="AL31" s="2"/>
       <c r="AM31" s="2"/>
+      <c r="AN31" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="32" spans="1:39">
+    <row r="32" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A32">
         <v>31</v>
       </c>
@@ -5742,8 +5867,11 @@
       <c r="AM32" s="2" t="s">
         <v>332</v>
       </c>
+      <c r="AN32" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="33" spans="1:39">
+    <row r="33" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A33">
         <v>32</v>
       </c>
@@ -5853,8 +5981,11 @@
       <c r="AK33" s="2"/>
       <c r="AL33" s="2"/>
       <c r="AM33" s="2"/>
+      <c r="AN33" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="34" spans="1:39">
+    <row r="34" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A34">
         <v>33</v>
       </c>
@@ -5966,8 +6097,11 @@
       </c>
       <c r="AL34" s="2"/>
       <c r="AM34" s="2"/>
+      <c r="AN34" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="35" spans="1:39">
+    <row r="35" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A35">
         <v>34</v>
       </c>
@@ -6077,8 +6211,11 @@
       <c r="AK35" s="2"/>
       <c r="AL35" s="2"/>
       <c r="AM35" s="2"/>
+      <c r="AN35" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="36" spans="1:39">
+    <row r="36" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A36">
         <v>35</v>
       </c>
@@ -6188,8 +6325,11 @@
       <c r="AK36" s="2"/>
       <c r="AL36" s="2"/>
       <c r="AM36" s="2"/>
+      <c r="AN36" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="37" spans="1:39">
+    <row r="37" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A37">
         <v>36</v>
       </c>
@@ -6299,8 +6439,11 @@
       <c r="AK37" s="2"/>
       <c r="AL37" s="2"/>
       <c r="AM37" s="2"/>
+      <c r="AN37" s="5">
+        <v>2</v>
+      </c>
     </row>
-    <row r="38" spans="1:39">
+    <row r="38" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A38">
         <v>37</v>
       </c>
@@ -6410,8 +6553,11 @@
       <c r="AK38" s="2"/>
       <c r="AL38" s="2"/>
       <c r="AM38" s="2"/>
+      <c r="AN38" s="5">
+        <v>6</v>
+      </c>
     </row>
-    <row r="39" spans="1:39">
+    <row r="39" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A39">
         <v>38</v>
       </c>
@@ -6521,8 +6667,11 @@
       <c r="AK39" s="2"/>
       <c r="AL39" s="2"/>
       <c r="AM39" s="2"/>
+      <c r="AN39" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="40" spans="1:39">
+    <row r="40" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A40">
         <v>39</v>
       </c>
@@ -6632,8 +6781,11 @@
       <c r="AK40" s="2"/>
       <c r="AL40" s="2"/>
       <c r="AM40" s="2"/>
+      <c r="AN40" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="41" spans="1:39">
+    <row r="41" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A41">
         <v>40</v>
       </c>
@@ -6749,8 +6901,11 @@
       <c r="AM41" s="2" t="s">
         <v>350</v>
       </c>
+      <c r="AN41" s="5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="42" spans="1:39">
+    <row r="42" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A42">
         <v>41</v>
       </c>
@@ -6862,8 +7017,11 @@
       </c>
       <c r="AL42" s="2"/>
       <c r="AM42" s="2"/>
+      <c r="AN42" s="5">
+        <v>7</v>
+      </c>
     </row>
-    <row r="43" spans="1:39">
+    <row r="43" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A43">
         <v>42</v>
       </c>
@@ -6979,8 +7137,11 @@
       <c r="AM43" s="2" t="s">
         <v>357</v>
       </c>
+      <c r="AN43" s="5">
+        <v>4</v>
+      </c>
     </row>
-    <row r="44" spans="1:39">
+    <row r="44" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A44">
         <v>43</v>
       </c>
@@ -7096,8 +7257,11 @@
       <c r="AM44" s="2" t="s">
         <v>363</v>
       </c>
+      <c r="AN44" s="5">
+        <v>9</v>
+      </c>
     </row>
-    <row r="45" spans="1:39">
+    <row r="45" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A45">
         <v>44</v>
       </c>
@@ -7213,8 +7377,11 @@
       <c r="AM45" s="2" t="s">
         <v>366</v>
       </c>
+      <c r="AN45" s="5">
+        <v>8</v>
+      </c>
     </row>
-    <row r="46" spans="1:39">
+    <row r="46" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A46">
         <v>45</v>
       </c>
@@ -7330,8 +7497,11 @@
       <c r="AM46" s="2" t="s">
         <v>371</v>
       </c>
+      <c r="AN46" s="5">
+        <v>10</v>
+      </c>
     </row>
-    <row r="47" spans="1:39">
+    <row r="47" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A47">
         <v>46</v>
       </c>
@@ -7447,8 +7617,11 @@
       <c r="AM47" s="2" t="s">
         <v>379</v>
       </c>
+      <c r="AN47" s="5">
+        <v>11</v>
+      </c>
     </row>
-    <row r="48" spans="1:39">
+    <row r="48" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A48">
         <v>47</v>
       </c>
@@ -7564,8 +7737,11 @@
       <c r="AM48" s="2" t="s">
         <v>384</v>
       </c>
+      <c r="AN48" s="5">
+        <v>1</v>
+      </c>
     </row>
-    <row r="49" spans="1:39">
+    <row r="49" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A49">
         <v>48</v>
       </c>
@@ -7675,8 +7851,11 @@
       <c r="AK49" s="2"/>
       <c r="AL49" s="2"/>
       <c r="AM49" s="2"/>
+      <c r="AN49" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="50" spans="1:39">
+    <row r="50" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A50">
         <v>49</v>
       </c>
@@ -7786,8 +7965,11 @@
       <c r="AK50" s="2"/>
       <c r="AL50" s="2"/>
       <c r="AM50" s="2"/>
+      <c r="AN50" s="5">
+        <v>3</v>
+      </c>
     </row>
-    <row r="51" spans="1:39">
+    <row r="51" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
       <c r="A51">
         <v>50</v>
       </c>
@@ -7903,9 +8085,12 @@
       <c r="AM51" s="2" t="s">
         <v>173</v>
       </c>
+      <c r="AN51" s="5">
+        <v>5</v>
+      </c>
     </row>
-    <row r="52" spans="1:39">
-      <c r="A52" s="4">
+    <row r="52" spans="1:40" hidden="1" x14ac:dyDescent="0.2">
+      <c r="A52">
         <v>51</v>
       </c>
       <c r="B52" s="1">
@@ -7930,10 +8115,10 @@
       <c r="I52" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J52" s="4" t="s">
+      <c r="J52" t="s">
         <v>68</v>
       </c>
-      <c r="K52" s="4" t="s">
+      <c r="K52" t="s">
         <v>142</v>
       </c>
       <c r="L52" s="2" t="s">
@@ -7978,13 +8163,13 @@
       <c r="Y52" s="2" t="s">
         <v>255</v>
       </c>
-      <c r="Z52" s="4" t="s">
+      <c r="Z52" t="s">
         <v>102</v>
       </c>
       <c r="AA52" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="AB52" s="4" t="s">
+      <c r="AB52" t="s">
         <v>55</v>
       </c>
       <c r="AC52" s="2" t="s">
@@ -7993,22 +8178,22 @@
       <c r="AD52" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AE52" s="4" t="s">
+      <c r="AE52" t="s">
         <v>80</v>
       </c>
-      <c r="AF52" s="4" t="s">
+      <c r="AF52" t="s">
         <v>80</v>
       </c>
-      <c r="AG52" s="4" t="s">
+      <c r="AG52" t="s">
         <v>107</v>
       </c>
-      <c r="AH52" s="4" t="s">
+      <c r="AH52" t="s">
         <v>215</v>
       </c>
-      <c r="AI52" s="4" t="s">
+      <c r="AI52" t="s">
         <v>80</v>
       </c>
-      <c r="AJ52" s="4" t="s">
+      <c r="AJ52" t="s">
         <v>110</v>
       </c>
       <c r="AK52" s="2" t="s">
@@ -8019,6 +8204,9 @@
       </c>
       <c r="AM52" s="2" t="s">
         <v>400</v>
+      </c>
+      <c r="AN52" s="5">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
